--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportTapeTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportTapeTemplate.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Tên sản phẩm</t>
   </si>
@@ -48,13 +48,19 @@
   </si>
   <si>
     <t>Ngày xuất hàng (đến)</t>
+  </si>
+  <si>
+    <t>Số lượng tape</t>
+  </si>
+  <si>
+    <t>Thành tiền</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -76,6 +82,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -113,12 +126,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -401,31 +417,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AMM1"/>
+  <dimension ref="A1:AMN1"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" style="1" customWidth="1"/>
     <col min="2" max="5" width="23" style="1" customWidth="1"/>
     <col min="6" max="6" width="18.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.85546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.85546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" style="1" customWidth="1"/>
-    <col min="12" max="13" width="14.5703125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" customWidth="1"/>
-    <col min="15" max="16" width="15" style="1" customWidth="1"/>
-    <col min="17" max="17" width="16" style="1" customWidth="1"/>
-    <col min="18" max="18" width="17.85546875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="16.7109375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="11.140625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="10" style="1" customWidth="1"/>
-    <col min="22" max="22" width="11" style="1" customWidth="1"/>
-    <col min="23" max="23" width="11.7109375" style="1" customWidth="1"/>
-    <col min="24" max="1027" width="9.140625" style="1"/>
+    <col min="7" max="8" width="22.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="18.42578125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" style="1" customWidth="1"/>
+    <col min="13" max="14" width="14.5703125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" customWidth="1"/>
+    <col min="16" max="17" width="15" style="1" customWidth="1"/>
+    <col min="18" max="18" width="16" style="1" customWidth="1"/>
+    <col min="19" max="19" width="17.85546875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="16.7109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="11.140625" style="1" customWidth="1"/>
+    <col min="22" max="22" width="10" style="1" customWidth="1"/>
+    <col min="23" max="23" width="11" style="1" customWidth="1"/>
+    <col min="24" max="24" width="11.7109375" style="1" customWidth="1"/>
+    <col min="25" max="1028" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1027" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10 1025:1028" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -448,12 +464,18 @@
         <v>2</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="AMJ1"/>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="AMK1"/>
       <c r="AML1"/>
       <c r="AMM1"/>
+      <c r="AMN1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportTapeTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportTapeTemplate.xlsx
@@ -420,7 +420,7 @@
   <dimension ref="A1:AMN1"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17" style="1" customWidth="1"/>
     <col min="2" max="5" width="23" style="1" customWidth="1"/>
     <col min="6" max="6" width="18.28515625" style="1" customWidth="1"/>
     <col min="7" max="8" width="22.140625" style="1" customWidth="1"/>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportTapeTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportTapeTemplate.xlsx
@@ -5,15 +5,18 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\23-kcvn-spm-be\src\main\kotlin\com\kcvn\spm\assets\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KCVN\23-kcvn-spm-be\src\main\kotlin\com\kcvn\spm\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Data" sheetId="2" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$J$1</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -60,19 +63,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="1"/>
     </font>
     <font>
@@ -126,15 +122,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -417,68 +410,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AMN1"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17" style="1" customWidth="1"/>
-    <col min="2" max="5" width="23" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" style="1" customWidth="1"/>
-    <col min="7" max="8" width="22.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="18.42578125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="19.85546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="17.42578125" style="1" customWidth="1"/>
-    <col min="13" max="14" width="14.5703125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" customWidth="1"/>
-    <col min="16" max="17" width="15" style="1" customWidth="1"/>
-    <col min="18" max="18" width="16" style="1" customWidth="1"/>
-    <col min="19" max="19" width="17.85546875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="16.7109375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="11.140625" style="1" customWidth="1"/>
-    <col min="22" max="22" width="10" style="1" customWidth="1"/>
-    <col min="23" max="23" width="11" style="1" customWidth="1"/>
-    <col min="24" max="24" width="11.7109375" style="1" customWidth="1"/>
-    <col min="25" max="1028" width="9.140625" style="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" customWidth="1"/>
+    <col min="9" max="9" width="19.42578125" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10 1025:1028" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AMK1"/>
-      <c r="AML1"/>
-      <c r="AMM1"/>
-      <c r="AMN1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <autoFilter ref="A1:J1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>